--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1442,7 +1442,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.composed[1]</t>
+          <t xml:space="preserve">ahead.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1467,14 +1467,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…認めない。…絶対に</t>
+          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.composed[1]</t>
+          <t xml:space="preserve">behind.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1499,14 +1499,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。…もういい</t>
+          <t xml:space="preserve">…勝手に幕を下ろすな。…まだ、こっちに残ってる</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…負けたけど…最高だった。…ありがとう</t>
+          <t xml:space="preserve">…っ…認めない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
@@ -1563,14 +1563,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。…あんたがいたから、ここまで来れた</t>
+          <t xml:space="preserve">…終わった。…もういい</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">loser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1595,14 +1595,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういい。…今日で終わりだ</t>
+          <t xml:space="preserve">…っ…負けたけど…最高だった。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.composed[1]</t>
+          <t xml:space="preserve">winner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1627,14 +1627,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来なよ。…全力で</t>
+          <t xml:space="preserve">…っ…ありがとう。…あんたがいたから、ここまで来れた</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1659,14 +1659,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………行くよ</t>
+          <t xml:space="preserve">…もういい。…今日で終わりだ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ええ。…行こう</t>
+          <t xml:space="preserve">…来なよ。…全力で</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういい。…リングで終わらせる</t>
+          <t xml:space="preserve">………行くよ</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1755,14 +1755,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いいよ。…来なよ</t>
+          <t xml:space="preserve">…ええ。…行こう</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.emotional.composed[1]</t>
+          <t xml:space="preserve">attacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1787,14 +1787,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと待ってた。…行くよ</t>
+          <t xml:space="preserve">…もういい。…リングで終わらせる</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.emotional.composed[1]</t>
+          <t xml:space="preserve">defender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1819,14 +1819,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来なよ。…全部受け止める</t>
+          <t xml:space="preserve">…いいよ。…来なよ</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1851,14 +1851,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…次は、こうはいかない</t>
+          <t xml:space="preserve">…ずっと待ってた。…行くよ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">fateDefender.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1883,14 +1883,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…でも、まだだ</t>
+          <t xml:space="preserve">…来なよ。…全部受け止める</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.emotional.composed[1]</t>
+          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、終わらない</t>
+          <t xml:space="preserve">…っ…次は、こうはいかない</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1947,14 +1947,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やっと。…でも、まだだよ。…まだ続くから</t>
+          <t xml:space="preserve">…勝った。…でも、まだだ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.composed[1]</t>
+          <t xml:space="preserve">fateLoser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1979,14 +1979,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しいね。…でも、次こそは</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、終わらない</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.composed[1]</t>
+          <t xml:space="preserve">fateWinner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2011,14 +2011,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…でもなんだろう、この感じ。…まだ終わらないね</t>
+          <t xml:space="preserve">…っ…やっと。…でも、まだだよ。…まだ続くから</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">loser.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…なんで。…こんなはずじゃ</t>
+          <t xml:space="preserve">…っ…悔しいね。…でも、次こそは</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2060,12 +2060,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">winner.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…ようやく</t>
+          <t xml:space="preserve">…勝った。…でもなんだろう、この感じ。…まだ終わらないね</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.emotional.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.emotional.composed[1]</t>
+          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が押し殺した声で{nameA}に告げた。「…もういい。…覚えてろ」</t>
+          <t xml:space="preserve">…っ…なんで。…こんなはずじゃ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2124,29 +2124,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[1]</t>
+          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。…すみません、まだ呑み込めません。</t>
+          <t xml:space="preserve">…っ…勝った。…ようやく</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2156,29 +2156,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[2]</t>
+          <t xml:space="preserve">awakening.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい、なんて言葉じゃ足りません。完敗です。</t>
+          <t xml:space="preserve">{nameB}が押し殺した声で{nameA}に告げた。「…もういい。…覚えてろ」</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[3]</t>
+          <t xml:space="preserve">composed_emotional.lose[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2203,14 +2203,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">届きませんでした。…すみません、声が震えて。</t>
+          <t xml:space="preserve">負けました。…すみません、まだ呑み込めません。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.petition[1]</t>
+          <t xml:space="preserve">composed_emotional.lose[2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2235,14 +2235,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人のことが、まだ腹の底に残ってます。やらせてください。</t>
+          <t xml:space="preserve">…悔しい、なんて言葉じゃ足りません。完敗です。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.lose[3]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.petition[2]</t>
+          <t xml:space="preserve">composed_emotional.lose[3]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと呑み込んできました。もう限界です。あいつと、やらせてください。</t>
+          <t xml:space="preserve">届きませんでした。…すみません、声が震えて。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.petition[3]</t>
+          <t xml:space="preserve">composed_emotional.petition[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…静かに言いますけど、本気です。あの人と、やらせてください。</t>
+          <t xml:space="preserve">社長。…あの人のことが、まだ腹の底に残ってます。やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.sendoff[1]</t>
+          <t xml:space="preserve">composed_emotional.petition[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2331,14 +2331,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。…この熱が冷めないうちに、行ってきます。</t>
+          <t xml:space="preserve">…ずっと呑み込んできました。もう限界です。あいつと、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.petition[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.sendoff[2]</t>
+          <t xml:space="preserve">composed_emotional.petition[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2363,14 +2363,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…感謝します。抑えてきた分、全部ぶつけてきます。</t>
+          <t xml:space="preserve">社長。…静かに言いますけど、本気です。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.sendoff[3]</t>
+          <t xml:space="preserve">composed_emotional.sendoff[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2395,14 +2395,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します。…行ってきます。震えは、止まりました。</t>
+          <t xml:space="preserve">ありがとうございます。…この熱が冷めないうちに、行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[1]</t>
+          <t xml:space="preserve">composed_emotional.sendoff[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2427,14 +2427,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。…社長、やっと胸のつかえが取れました。</t>
+          <t xml:space="preserve">…感謝します。抑えてきた分、全部ぶつけてきます。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.sendoff[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[2]</t>
+          <t xml:space="preserve">composed_emotional.sendoff[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2459,14 +2459,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。…社長、感謝します。言葉が、まとまらない。</t>
+          <t xml:space="preserve">感謝します。…行ってきます。震えは、止まりました。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[3]</t>
+          <t xml:space="preserve">composed_emotional.win[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。…叫びたいのを、こらえてます。</t>
+          <t xml:space="preserve">勝ちました。…社長、やっと胸のつかえが取れました。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional._accept[1]</t>
+          <t xml:space="preserve">composed_emotional.win[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅん。よく、わたしの名前を出せたね。</t>
+          <t xml:space="preserve">勝ちました。…社長、感謝します。言葉が、まとまらない。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_emotional.win[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional._accept[2]</t>
+          <t xml:space="preserve">composed_emotional.win[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいよ。言葉はいらない。来なよ。</t>
+          <t xml:space="preserve">勝てました。…叫びたいのを、こらえてます。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional._accept[3]</t>
+          <t xml:space="preserve">composed_emotional._accept[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2587,14 +2587,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう。じゃあ、覚悟はできてるんだ。</t>
+          <t xml:space="preserve">……ふぅん。よく、わたしの名前を出せたね。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.draw[1]</t>
+          <t xml:space="preserve">composed_emotional._accept[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2619,14 +2619,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……終わってない。まだ、全然。</t>
+          <t xml:space="preserve">……いいよ。言葉はいらない。来なよ。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional._accept[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.draw[2]</t>
+          <t xml:space="preserve">composed_emotional._accept[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……こんな中途半端、いちばん腹が立つ。</t>
+          <t xml:space="preserve">……そう。じゃあ、覚悟はできてるんだ。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.draw[3]</t>
+          <t xml:space="preserve">composed_emotional.draw[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2683,14 +2683,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次だ。次は、必ず終わらせる。</t>
+          <t xml:space="preserve">……終わってない。まだ、全然。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[1]</t>
+          <t xml:space="preserve">composed_emotional.draw[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちっ。次は、こうはいかない。</t>
+          <t xml:space="preserve">……こんな中途半端、いちばん腹が立つ。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.draw[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[2]</t>
+          <t xml:space="preserve">composed_emotional.draw[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……そうかよ。覚えておく。</t>
+          <t xml:space="preserve">……次だ。次は、必ず終わらせる。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.lose[3]</t>
+          <t xml:space="preserve">composed_emotional.lose[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2779,14 +2779,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何も言わない。今は、何も。</t>
+          <t xml:space="preserve">……ちっ。次は、こうはいかない。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[1]</t>
+          <t xml:space="preserve">composed_emotional.lose[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2811,14 +2811,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これで分かった? 次はないよ。</t>
+          <t xml:space="preserve">……っ……そうかよ。覚えておく。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.lose[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[2]</t>
+          <t xml:space="preserve">composed_emotional.lose[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2843,14 +2843,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……言いたいことは、全部言えたよ。</t>
+          <t xml:space="preserve">……何も言わない。今は、何も。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_emotional.win[3]</t>
+          <t xml:space="preserve">composed_emotional.win[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2875,14 +2875,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、名前は呼ばないほうがいい。</t>
+          <t xml:space="preserve">……これで分かった? 次はないよ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.emotional.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2892,29 +2892,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.emotional.composed[1]</t>
+          <t xml:space="preserve">composed_emotional.win[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…もう少しだけ、やってみる</t>
+          <t xml:space="preserve">……言いたいことは、全部言えたよ。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_emotional.win[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2924,29 +2924,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">composed_emotional.win[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あのベルト、もう一度。……触りたい</t>
+          <t xml:space="preserve">……もう、名前は呼ばないほうがいい。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.emotional.composed[1]</t>
+          <t xml:space="preserve">accepted.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2971,14 +2971,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…まだ必要としてくれるんだ。…わかった、やるよ</t>
+          <t xml:space="preserve">…っ…行かせて、ほしい。…頼むよ</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.emotional.composed[1]</t>
+          <t xml:space="preserve">accepted.emotional.composed[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…もう少しだけ、頑張る</t>
+          <t xml:space="preserve">…っ、ごめん。…でも、行かなきゃいけないんだ</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">defended.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3035,14 +3035,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、持てたから。……十分</t>
+          <t xml:space="preserve">…っ、残っていいんだ。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">defended.emotional.composed[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3067,14 +3067,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…もういい。…わかった</t>
+          <t xml:space="preserve">…っ…嬉しいよ。…本当に</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.emotional.composed[1]</t>
+          <t xml:space="preserve">defense_failed.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3099,14 +3099,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…覚悟はできてたよ</t>
+          <t xml:space="preserve">…っ、ごめん。…本当に、ごめん</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.emotional.composed[1]</t>
+          <t xml:space="preserve">defense_failed.emotional.composed[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…わかってた。…うん</t>
+          <t xml:space="preserve">…っ…許してほしい。…勝手だけど</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.emotional.composed[1]</t>
+          <t xml:space="preserve">default.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝てなくなった、か。……うん</t>
+          <t xml:space="preserve">……うん。…もう少しだけ、やってみる</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">former_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…このベルトは渡さない。…まだ闘える</t>
+          <t xml:space="preserve">…あのベルト、もう一度。……触りたい</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.emotional.composed[1]</t>
+          <t xml:space="preserve">heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3227,14 +3227,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…何年ここにいたと思ってるの</t>
+          <t xml:space="preserve">…っ、…まだ必要としてくれるんだ。…わかった、やるよ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.emotional.composed[1]</t>
+          <t xml:space="preserve">high_trust.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3259,14 +3259,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…まだ闘いたい。…お願い、もう少しだけ</t>
+          <t xml:space="preserve">……ありがとう。…もう少しだけ、頑張る</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3291,14 +3291,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、…冗談じゃない。…まだ終わらないよ</t>
+          <t xml:space="preserve">…ベルト、持てたから。……十分</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…返したくなかった。…でも、ありがとう</t>
+          <t xml:space="preserve">…っ、…もういい。…わかった</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3355,14 +3355,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…欲しかったな。…でも、よかったよ</t>
+          <t xml:space="preserve">……ありがとう。…覚悟はできてたよ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…泣くなって。…こっちまで、困るだろ</t>
+          <t xml:space="preserve">…っ、…わかってた。…うん</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_winless.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここが全部だった。…ありがとう</t>
+          <t xml:space="preserve">…勝てなくなった、か。……うん</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3451,14 +3451,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…こんなところで。…まだ、始まったばかりなのに</t>
+          <t xml:space="preserve">…っ、…このベルトは渡さない。…まだ闘える</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3483,14 +3483,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しいよ。…これからだったのに</t>
+          <t xml:space="preserve">…っ、…何年ここにいたと思ってるの</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3515,14 +3515,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…わかってたよ。…でも、寂しいもんだね</t>
+          <t xml:space="preserve">…っ、…まだ闘いたい。…お願い、もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…返したくない。…まだ、このベルト…</t>
+          <t xml:space="preserve">…っ、…冗談じゃない。…まだ終わらないよ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">A1_champion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3579,14 +3579,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが好きだから。…それだけだよ</t>
+          <t xml:space="preserve">…っ…返したくなかった。…でも、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3596,29 +3596,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ…ありがとう…ございます。…絶対、返すから…。</t>
+          <t xml:space="preserve">…っ…欲しかったな。…でも、よかったよ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3628,29 +3628,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">A3_heel.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りない…けど…っ。…気持ちは、受け取ったから…。</t>
+          <t xml:space="preserve">…っ…泣くなって。…こっちまで、困るだろ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やっぱり…っ…。……分かった…。</t>
+          <t xml:space="preserve">…っ…ここが全部だった。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3692,29 +3692,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional.composed[1]</t>
+          <t xml:space="preserve">B1_young.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}{record}……悔しくないって言ったら、嘘になるかな…っ。</t>
+          <t xml:space="preserve">…っ…こんなところで。…まだ、始まったばかりなのに</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3724,29 +3724,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">B2_prime.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ…。…分かった…。…悔しく、ないから…。</t>
+          <t xml:space="preserve">…っ…悔しいよ。…これからだったのに</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3756,29 +3756,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional.composed[1]</t>
+          <t xml:space="preserve">B3_older.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ。{tenure}…ここにいたかった…けど…もう、いられない…。</t>
+          <t xml:space="preserve">…っ…わかってたよ。…でも、寂しいもんだね</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3788,478 +3788,478 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ…。…ありがとう…。…必ず、返すから…。</t>
+          <t xml:space="preserve">…っ…返したくない。…まだ、このベルト…</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここが好きだから。…それだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_accept.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…っ…ありがとう…ございます。…絶対、返すから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_accept.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りない…けど…っ。…気持ちは、受け取ったから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……やっぱり…っ…。……分かった…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。{tenure}{record}……悔しくないって言ったら、嘘になるかな…っ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……っ…。…分かった…。…悔しく、ないから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もういいよ。何も言う気はない。……さよなら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい。…けど、もうここにはいられないんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…自分でも、どうしたいのか分からない。…ただ、このままじゃダメだって、それだけは。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…っ。{tenure}…ここにいたかった…けど…もう、いられない…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{tenure_farewell}…ここでの時間は、忘れないよ。{rivalry}…じゃあ、さよなら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。…ありがとう。…でも…もう、戻れないんだ。…ごめん。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…っ…。…ありがとう…。…必ず、返すから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional.composed[1]</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="D123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.emotional.composed[1]</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr" s="2">
+      <c r="E123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr" s="3">
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここが好きなんだ。
 …悪いけど、その話は聞けない</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fail.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ごめん。今は離れられない</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…引き抜き。…ふぅん。…聞くよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.emotional.composed[1]</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…っ…新しい場所か。…頑張るよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの子たち、ちゃんと抱えていてください。お願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメインは私たちに任せてください。今の状態を逃したくないんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちが受け取っているもの、もう一度見直してください。お願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーがやってきたこと、しっかり見ていただきたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。引き受けた重さ、噛み締めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…そうですか。…次は、必ず。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
-        </is>
-      </c>
-    </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4269,29 +4269,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">fail.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…この決断、忘れません。ありがとうございます。</t>
+          <t xml:space="preserve">…ごめん。今は離れられない</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4301,29 +4301,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">start.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…次に、また。</t>
+          <t xml:space="preserve">…引き抜き。…ふぅん。…聞くよ</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4333,29 +4333,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
+          <t xml:space="preserve">success.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
+          <t xml:space="preserve">…っ…新しい場所か。…頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
+          <t xml:space="preserve">社長、私たちの子たち、ちゃんと抱えていてください。お願いします。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4412,14 +4412,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
+          <t xml:space="preserve">社長、次のメインは私たちに任せてください。今の状態を逃したくないんです。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4444,14 +4444,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
+          <t xml:space="preserve">社長、私たちが受け取っているもの、もう一度見直してください。お願いします。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ、…そうでしたか。…悪いことをしました。</t>
+          <t xml:space="preserve">社長、私たちのメンバーがやってきたこと、しっかり見ていただきたい。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4508,14 +4508,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないですね。</t>
+          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですね、…悪かったです。</t>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。引き受けた重さ、噛み締めます。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4636,14 +4636,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私、止まれませんから。</t>
+          <t xml:space="preserve">…そうですか。…次は、必ず。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、申し訳ありません。…次こそ、ちゃんと出ます。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4700,14 +4700,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。</t>
+          <t xml:space="preserve">社長…この決断、忘れません。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…申し訳ないです、ありがたいです。</t>
+          <t xml:space="preserve">…そうですか。…次に、また。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…見ていてくださったんですね。ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。…まだ、立っていられます。</t>
+          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。一人で抱えなくていいんですね。</t>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…私の至らなさ、噛み締めます。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ああ、…そうでしたか。…悪いことをしました。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形で気にかけてくださるの、ありがたいです。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないですね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4956,14 +4956,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…私が、抑えきれていませんでした。</t>
+          <t xml:space="preserve">…そうですね、…悪かったです。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…一度息を吸って、結局何も言わなかった）</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
+          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5052,14 +5052,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そうですね。…私が、追い込みすぎていました。</t>
+          <t xml:space="preserve">…ありがとうございます。…私、止まれませんから。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。やり切らせてください。</t>
+          <t xml:space="preserve">…社長、申し訳ありません。…次こそ、ちゃんと出ます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。私、見えていませんでした。</t>
+          <t xml:space="preserve">…社長…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許せないね、あのやり方は</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…申し訳ないです、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらも、引けないんだ</t>
+          <t xml:space="preserve">…社長…見ていてくださったんですね。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5197,29 +5197,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか壁を超えてみたいな。…へぇ、イイ感じじゃん♪</t>
+          <t xml:space="preserve">…大丈夫です。…まだ、立っていられます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5229,29 +5229,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…っ…体が、勝手に——…悪くない——）</t>
+          <t xml:space="preserve">…社長…ありがとうございます。一人で抱えなくていいんですね。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5261,29 +5261,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう伸びないんだ。…ちょっと寂しいけど、悪くない</t>
+          <t xml:space="preserve">…そうですか。…私の至らなさ、噛み締めます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5293,29 +5293,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れた…ちょっとだけ、ジーンと来ちゃった</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5325,29 +5325,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ちょっと嬉しいかも…へへ</t>
+          <t xml:space="preserve">…社長…そういう形で気にかけてくださるの、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5357,29 +5357,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あはは、ダメだ。嬉しすぎて言葉にならない</t>
+          <t xml:space="preserve">…そうですか。…私が、抑えきれていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5389,29 +5389,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、こんなに見てくれてるんだ…ちょっと照れちゃうね</t>
+          <t xml:space="preserve">（…一度息を吸って、結局何も言わなかった）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5421,29 +5421,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あぁ…ダメだ、こんなに応援されたら…泣いちゃう</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5453,29 +5453,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いいかな。…何もしたくない</t>
+          <t xml:space="preserve">…社長…そうですね。…私が、追い込みすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5485,29 +5485,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…また闘いたい。…大丈夫、もう大丈夫だ</t>
+          <t xml:space="preserve">…ありがとうございます。やり切らせてください。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5517,29 +5517,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やっと…抜け出せた。…もう大丈夫</t>
+          <t xml:space="preserve">…社長…ありがとうございます。私、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.composed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5549,29 +5549,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.attack.composed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…あの負けが…まだ、引っかかってる</t>
+          <t xml:space="preserve">許せないね、あのやり方は</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.composed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5581,29 +5581,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.defend.composed</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…治ったのに。…なんで動けないんだ</t>
+          <t xml:space="preserve">こちらも、引けないんだ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…戻ってきた。…けど、体が少し…震える</t>
+          <t xml:space="preserve">なんだか壁を超えてみたいな。…へぇ、イイ感じじゃん♪</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5660,14 +5660,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…治ったのに。…この不安は何だろう</t>
+          <t xml:space="preserve">（…っ…体が、勝手に——…悪くない——）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5677,29 +5677,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">fresh.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
+          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5709,29 +5709,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">heavy.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
+          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5741,29 +5741,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.emotional.composed[1]</t>
+          <t xml:space="preserve">warm.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
+          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5773,29 +5773,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.emotional.composed[1]</t>
+          <t xml:space="preserve">cap_reached.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
+          <t xml:space="preserve">…もう伸びないんだ。…ちょっと寂しいけど、悪くない</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5805,29 +5805,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.emotional.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
+          <t xml:space="preserve">ここまで来れた…ちょっとだけ、ジーンと来ちゃった</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5837,29 +5837,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…言葉になりません</t>
+          <t xml:space="preserve">わ、ちょっと嬉しいかも…へへ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5869,29 +5869,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">ovr_legend.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
+          <t xml:space="preserve">…あはは、ダメだ。嬉しすぎて言葉にならない</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5901,29 +5901,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">pop_growth.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合にします。絶対に</t>
+          <t xml:space="preserve">わ、こんなに見てくれてるんだ…ちょっと照れちゃうね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5933,29 +5933,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">pop_star.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
+          <t xml:space="preserve">あぁ…ダメだ、こんなに応援されたら…泣いちゃう</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5965,29 +5965,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
+          <t xml:space="preserve">…っ…もう、いいかな。…何もしたくない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5997,29 +5997,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます、本当に</t>
+          <t xml:space="preserve">…っ…また闘いたい。…大丈夫、もう大丈夫だ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6029,29 +6029,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった</t>
+          <t xml:space="preserve">…っ…やっと…抜け出せた。…もう大丈夫</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6061,29 +6061,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">defeat.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いい</t>
+          <t xml:space="preserve">…っ…あの負けが…まだ、引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6093,29 +6093,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
+          <t xml:space="preserve">…っ…治ったのに。…なんで動けないんだ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6125,29 +6125,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
+          <t xml:space="preserve">…っ…戻ってきた。…けど、体が少し…震える</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6157,29 +6157,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">penalty_end.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出番、まだかな</t>
+          <t xml:space="preserve">…っ…治ったのに。…この不安は何だろう</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6189,29 +6189,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">bestMatch.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いいさ</t>
+          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6221,29 +6221,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.emotional.composed[1]</t>
+          <t xml:space="preserve">champion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…{name2}。…元気で</t>
+          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6253,29 +6253,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
+          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">mvp.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…次は、こうはいかない</t>
+          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6317,29 +6317,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">rookie.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
@@ -6359,19 +6359,19 @@
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
+          <t xml:space="preserve">ドーム。…言葉になりません</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6381,29 +6381,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
+          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6413,29 +6413,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">いい試合にします。絶対に</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
@@ -6455,19 +6455,19 @@
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6477,29 +6477,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6509,29 +6509,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
+          <t xml:space="preserve">…ありがとうございます、本当に</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6541,29 +6541,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional.composed[1]</t>
+          <t xml:space="preserve">N1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
+          <t xml:space="preserve">…っ、練習が楽しい。…もっとやりたいな</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6573,29 +6573,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.emotional.composed[1]</t>
+          <t xml:space="preserve">N1.emotional.composed[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">…体が動くようになってきた。…嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.emotional.composed[1]</t>
+          <t xml:space="preserve">N2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…みんなのこと、好きだよ。…一緒にいられて幸せだ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional.composed[1]</t>
+          <t xml:space="preserve">N3.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…体がしんどいな。…でも、まだやりたいんだけど</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6669,29 +6669,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional.composed[1]</t>
+          <t xml:space="preserve">N4.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+          <t xml:space="preserve">…みんな応援してくれてるんだね。…ちょっと、泣きそうだ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6701,29 +6701,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">N5_low.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+          <t xml:space="preserve">…もう、わからない。…どうすればいいんだろうね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6733,29 +6733,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">N5_warning.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…最近、ずっと晴れないんだよね。…うまく言えないけど</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6765,29 +6765,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.emotional.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…っ…ここにいてよかった</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6797,29 +6797,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">G1.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…っ…まあ、いい</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6829,29 +6829,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.emotional.composed[1]</t>
+          <t xml:space="preserve">G2.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6861,29 +6861,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">G3.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6893,29 +6893,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">G4.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+          <t xml:space="preserve">…っ…出番、まだかな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6925,29 +6925,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">R2.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…っ…まあ、いいさ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6957,29 +6957,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">R3.modal.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…っ…{name2}。…元気で</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6989,29 +6989,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">R4.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7021,29 +7021,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">R5.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…次は、こうはいかない</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7053,29 +7053,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いい</t>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7085,29 +7085,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">faction_decree.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
+          <t xml:space="preserve">……参ったな。これは、こたえるよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7117,29 +7117,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">E1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
+          <t xml:space="preserve">…テレビか。…っ、…嬉しいね。やらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7149,29 +7149,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">E6.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。…どうしたものかな。正直、迷ってる</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7181,29 +7181,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">S_boycott.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
+          <t xml:space="preserve">…もう無理だよ。…今日は、やらない</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.composed[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7213,29 +7213,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">S_boycott.emotional.composed[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
+          <t xml:space="preserve">…出してもらえないのに練習して。…何になるのかな</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7245,29 +7245,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">S_grumble.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…超える。…必ず</t>
+          <t xml:space="preserve">（感情を押し殺した声で「…もう限界かもね」と仲間にだけ漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7277,29 +7277,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">S_sns.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
+          <t xml:space="preserve">（SNSに涙の絵文字と「…もう駄目かもしれないね」と投稿。静かな文面だけに騒ぎが大きくなっている）</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7309,29 +7309,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">S1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
+          <t xml:space="preserve">…頼むよ。ベルト、挑ませてほしい。…もう、待てないんだ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7341,29 +7341,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">S2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いいかな</t>
+          <t xml:space="preserve">…あの人と、やらせてほしい。…これだけは、譲れないんだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7373,29 +7373,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">S3.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大丈夫、かな</t>
+          <t xml:space="preserve">…すまない。体が、もう限界でさ。…少し休ませてほしい</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">S4_direct.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
+          <t xml:space="preserve">…もう無理だよ。…このままなら、ここにはいられない</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7437,29 +7437,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">S4_silent.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
+          <t xml:space="preserve">……っ（込み上げたものを飲み下し、静かに目を閉じた）</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7469,29 +7469,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[2]</t>
+          <t xml:space="preserve">S5.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
+          <t xml:space="preserve">…頼むよ。特訓させてほしい。…まだ、こんなもので終われないんだ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7501,29 +7501,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">S6.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
+          <t xml:space="preserve">…後輩に残せるものがあるなら、やらせてほしい。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7533,29 +7533,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[2]</t>
+          <t xml:space="preserve">B1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
+          <t xml:space="preserve">…っ…すぐ治す。…早く戻りたいんだ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7565,29 +7565,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
+          <t xml:space="preserve">…もう無理だよ。…あの人といると、息が詰まる</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7597,29 +7597,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.composed[2]</t>
+          <t xml:space="preserve">B2_fighter2.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
+          <t xml:space="preserve">…私だって辛いんだよ。…わかってないだろうけど</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7629,29 +7629,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_brand.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利だ。一人では……ここには、到底たどり着けなかった</t>
+          <t xml:space="preserve">…っ…コラボか。…どんな形になるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7661,29 +7661,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[2]</t>
+          <t xml:space="preserve">B4_cm.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた道を……最後まで歩けた。それが、何より……</t>
+          <t xml:space="preserve">…っ…CMか。…緊張はする。…でもやるよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7693,29 +7693,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_fan.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は受け取ろう……だが、この胸の内は……次に晴らす他ない</t>
+          <t xml:space="preserve">…っ…みんなに会えるんだ。…全員、笑顔にして帰すよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7725,29 +7725,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.composed[2]</t>
+          <t xml:space="preserve">B4_fashion.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった……それだけが、今は重い。次こそ……全てを</t>
+          <t xml:space="preserve">…っ…ランウェイか。…これは、緊張するやつだね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7757,29 +7757,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も訪れた。それでも……足が前に出た。理屈ではなく、意地だった</t>
+          <t xml:space="preserve">…っ…グラビア。…私が、か。…参ったな</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7789,29 +7789,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.composed[2]</t>
+          <t xml:space="preserve">B4_variety.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は壊れかけている。だが……最後に立っていた。それだけで、十分だ</t>
+          <t xml:space="preserve">…っ…バラエティか。…これは、少し楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7821,29 +7821,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">B4.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
+          <t xml:space="preserve">…っ…私が、か。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7853,29 +7853,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
+          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7885,29 +7885,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
+          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7917,29 +7917,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7949,29 +7949,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7981,29 +7981,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">emotional.composed[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。…負けない</t>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8013,29 +8013,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…やるよ</t>
+          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8045,29 +8045,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けない。…絶対に</t>
+          <t xml:space="preserve">…勝手に幕を下ろすな。…まだ、こっちに残ってる</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8077,29 +8077,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">draftInterest.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
+          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8109,29 +8109,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">draftJoin.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝負しよう。…本気で</t>
+          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8141,29 +8141,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">faGreeting.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8173,29 +8173,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.composed[1]</t>
+          <t xml:space="preserve">faSigning.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8205,29 +8205,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.composed[1]</t>
+          <t xml:space="preserve">faWelcome.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…よかった</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8237,59 +8237,1851 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…もう、いい</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…超える。…必ず</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…もう、いいかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…大丈夫、かな</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人の勝利だ。一人では……ここには、到底たどり着けなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間が繋いでくれた道を……最後まで歩けた。それが、何より……</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賞は受け取ろう……だが、この胸の内は……次に晴らす他ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足りなかった……それだけが、今は重い。次こそ……全てを</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">限界は何度も訪れた。それでも……足が前に出た。理屈ではなく、意地だった</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.emotional.composed[2]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は壊れかけている。だが……最後に立っていた。それだけで、十分だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…行くよ。…負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…選ばれたか。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けない。…絶対に</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝負しよう。…本気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.emotional.composed[1]</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr" s="2">
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr" s="12">
+      <c r="D303" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.emotional.composed[1]</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr" s="2">
+      <c r="E303" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr" s="3">
+      <c r="F303" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
         </is>
       </c>
     </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">emotional.composed[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H249"/>
+  <autoFilter ref="A1:H305"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -354,7 +354,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -369,7 +369,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.composed[1]</t>
+          <t xml:space="preserve">atk.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -386,7 +386,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -401,7 +401,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.composed[2]</t>
+          <t xml:space="preserve">atk.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -418,7 +418,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -433,7 +433,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.composed[3]</t>
+          <t xml:space="preserve">atk.composed.emotional[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -450,7 +450,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.emotional.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.emotional[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -465,7 +465,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.emotional.composed[4]</t>
+          <t xml:space="preserve">atk.composed.emotional[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -482,7 +482,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -497,7 +497,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -514,7 +514,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -529,7 +529,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -546,7 +546,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.emotional.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -561,7 +561,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.emotional.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.emotional[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -578,7 +578,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -593,7 +593,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.composed[1]</t>
+          <t xml:space="preserve">climax.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -610,7 +610,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.emotional.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -625,7 +625,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.emotional.composed[2]</t>
+          <t xml:space="preserve">climax.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -642,7 +642,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -657,7 +657,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">badWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -674,7 +674,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">goodWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -706,7 +706,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.emotional.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -721,7 +721,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.emotional.composed[1]</t>
+          <t xml:space="preserve">competition_won.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -738,7 +738,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.emotional.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -753,7 +753,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.emotional.composed[1]</t>
+          <t xml:space="preserve">direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -770,7 +770,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.emotional.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -785,7 +785,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.emotional.composed[1]</t>
+          <t xml:space="preserve">fa_signing.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -802,7 +802,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.emotional.hit[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -817,7 +817,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed.hit[1]</t>
+          <t xml:space="preserve">composed.emotional.hit[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -834,7 +834,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.emotional.hit[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -849,7 +849,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed.hit[2]</t>
+          <t xml:space="preserve">composed.emotional.hit[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -866,7 +866,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.emotional.win[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed.win[1]</t>
+          <t xml:space="preserve">composed.emotional.win[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -898,7 +898,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.emotional.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.emotional.win[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -913,7 +913,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed.win[2]</t>
+          <t xml:space="preserve">composed.emotional.win[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -930,7 +930,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -945,7 +945,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -962,7 +962,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -977,7 +977,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -994,7 +994,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1026,7 +1026,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1058,7 +1058,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1090,7 +1090,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1122,7 +1122,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1154,7 +1154,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1186,7 +1186,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1218,7 +1218,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1250,7 +1250,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1282,7 +1282,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1314,7 +1314,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1346,7 +1346,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1378,7 +1378,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1410,7 +1410,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1442,7 +1442,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.emotional.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1474,7 +1474,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.emotional.composed[1]</t>
+          <t xml:space="preserve">behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1506,7 +1506,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.composed[1]</t>
+          <t xml:space="preserve">loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1538,7 +1538,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.composed[1]</t>
+          <t xml:space="preserve">winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1570,7 +1570,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.composed[1]</t>
+          <t xml:space="preserve">loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1602,7 +1602,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.composed[1]</t>
+          <t xml:space="preserve">winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1634,7 +1634,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1666,7 +1666,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.composed[1]</t>
+          <t xml:space="preserve">defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1698,7 +1698,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1730,7 +1730,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.composed[1]</t>
+          <t xml:space="preserve">defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1762,7 +1762,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.emotional.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1794,7 +1794,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.emotional.composed[1]</t>
+          <t xml:space="preserve">defender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1826,7 +1826,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.emotional.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1858,7 +1858,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.emotional.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1890,7 +1890,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1922,7 +1922,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1954,7 +1954,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.emotional.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1986,7 +1986,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.emotional.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2018,7 +2018,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.emotional.composed[1]</t>
+          <t xml:space="preserve">loser.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2050,7 +2050,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.emotional.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.emotional.composed[1]</t>
+          <t xml:space="preserve">winner.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2082,7 +2082,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.emotional.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2114,7 +2114,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.emotional.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2146,7 +2146,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.emotional.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.emotional.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2946,7 +2946,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2978,7 +2978,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.emotional.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.emotional.composed[2]</t>
+          <t xml:space="preserve">accepted.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3010,7 +3010,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional.composed[1]</t>
+          <t xml:space="preserve">defended.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3042,7 +3042,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.emotional.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.emotional.composed[2]</t>
+          <t xml:space="preserve">defended.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3074,7 +3074,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3106,7 +3106,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.emotional.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.emotional.composed[2]</t>
+          <t xml:space="preserve">defense_failed.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3138,7 +3138,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.emotional.composed[1]</t>
+          <t xml:space="preserve">default.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3170,7 +3170,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3202,7 +3202,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.emotional.composed[1]</t>
+          <t xml:space="preserve">heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3234,7 +3234,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.emotional.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.emotional.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3266,7 +3266,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3298,7 +3298,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3330,7 +3330,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3362,7 +3362,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3394,7 +3394,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.emotional.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3426,7 +3426,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3458,7 +3458,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3490,7 +3490,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3522,7 +3522,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3554,7 +3554,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.emotional.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3586,7 +3586,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.emotional.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3618,7 +3618,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.emotional.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3650,7 +3650,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.emotional.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3682,7 +3682,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.emotional.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3714,7 +3714,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.emotional.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3746,7 +3746,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.emotional.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3778,7 +3778,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.emotional.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3810,7 +3810,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3842,7 +3842,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3874,7 +3874,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.emotional.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3906,7 +3906,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3938,7 +3938,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.emotional.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3970,7 +3970,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.emotional.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4002,7 +4002,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4034,7 +4034,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.emotional.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.emotional.composed[2]</t>
+          <t xml:space="preserve">sudden_departure.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4066,7 +4066,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.emotional.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4098,7 +4098,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.emotional.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4130,7 +4130,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.emotional.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4162,7 +4162,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.emotional.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4194,7 +4194,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.emotional.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.emotional.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.emotional.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.emotional.composed[1]</t>
+          <t xml:space="preserve">blocked.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4259,7 +4259,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.emotional.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.emotional.composed[1]</t>
+          <t xml:space="preserve">fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4291,7 +4291,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.emotional.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.emotional.composed[1]</t>
+          <t xml:space="preserve">start.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4323,7 +4323,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.emotional.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.emotional.composed[1]</t>
+          <t xml:space="preserve">success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -5603,7 +5603,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5635,7 +5635,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5667,7 +5667,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.emotional.composed[1]</t>
+          <t xml:space="preserve">fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5699,7 +5699,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.emotional.composed[1]</t>
+          <t xml:space="preserve">heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5731,7 +5731,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.emotional.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.emotional.composed[1]</t>
+          <t xml:space="preserve">warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5763,7 +5763,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.emotional.composed[1]</t>
+          <t xml:space="preserve">cap_reached.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5795,7 +5795,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.emotional.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5827,7 +5827,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5859,7 +5859,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.emotional.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5891,7 +5891,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.emotional.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5923,7 +5923,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.emotional.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.emotional.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5955,7 +5955,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5987,7 +5987,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6019,7 +6019,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.emotional.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6083,7 +6083,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6115,7 +6115,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.emotional.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6147,7 +6147,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.emotional.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.emotional.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6179,7 +6179,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6211,7 +6211,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6243,7 +6243,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.emotional.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6275,7 +6275,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.emotional.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6307,7 +6307,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.emotional.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.emotional.composed[1]</t>
+          <t xml:space="preserve">rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6339,7 +6339,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6371,7 +6371,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6403,7 +6403,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6435,7 +6435,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6467,7 +6467,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[2]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6499,7 +6499,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.emotional.composed[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[3]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6531,7 +6531,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.composed[1]</t>
+          <t xml:space="preserve">N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6563,7 +6563,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.emotional.composed[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.emotional.composed[2]</t>
+          <t xml:space="preserve">N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6595,7 +6595,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.emotional.composed[1]</t>
+          <t xml:space="preserve">N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6627,7 +6627,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.emotional.composed[1]</t>
+          <t xml:space="preserve">N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6659,7 +6659,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.emotional.composed[1]</t>
+          <t xml:space="preserve">N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6691,7 +6691,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.emotional.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6723,7 +6723,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.emotional.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.emotional.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6755,7 +6755,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6787,7 +6787,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6819,7 +6819,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6851,7 +6851,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6883,7 +6883,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6915,7 +6915,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6947,7 +6947,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.emotional.composed[1]</t>
+          <t xml:space="preserve">R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6979,7 +6979,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7011,7 +7011,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7043,7 +7043,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.emotional.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7075,7 +7075,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.emotional.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.emotional.composed[1]</t>
+          <t xml:space="preserve">faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7107,7 +7107,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.emotional.composed[1]</t>
+          <t xml:space="preserve">E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7139,7 +7139,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.emotional.composed[1]</t>
+          <t xml:space="preserve">E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7171,7 +7171,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7203,7 +7203,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.emotional.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.emotional.composed[2]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7235,7 +7235,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.emotional.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7267,7 +7267,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.emotional.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7299,7 +7299,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.emotional.composed[1]</t>
+          <t xml:space="preserve">S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7331,7 +7331,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.emotional.composed[1]</t>
+          <t xml:space="preserve">S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7363,7 +7363,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.emotional.composed[1]</t>
+          <t xml:space="preserve">S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7395,7 +7395,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.emotional.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.emotional.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7459,7 +7459,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.emotional.composed[1]</t>
+          <t xml:space="preserve">S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7491,7 +7491,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.emotional.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.emotional.composed[1]</t>
+          <t xml:space="preserve">S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7523,7 +7523,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.emotional.composed[1]</t>
+          <t xml:space="preserve">B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7555,7 +7555,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.emotional.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7587,7 +7587,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.emotional.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7619,7 +7619,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7651,7 +7651,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7683,7 +7683,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7715,7 +7715,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7747,7 +7747,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7779,7 +7779,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.emotional.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7811,7 +7811,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.emotional.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.emotional.composed[1]</t>
+          <t xml:space="preserve">B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7843,7 +7843,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7875,7 +7875,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7907,7 +7907,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7939,7 +7939,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7971,7 +7971,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8003,7 +8003,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.emotional.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8035,7 +8035,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.emotional.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8067,7 +8067,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.emotional.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8099,7 +8099,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional.composed[1]</t>
+          <t xml:space="preserve">draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8131,7 +8131,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.emotional.composed[1]</t>
+          <t xml:space="preserve">faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8195,7 +8195,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.emotional.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8227,7 +8227,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.emotional.composed[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8259,7 +8259,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.emotional.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8291,7 +8291,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.emotional.composed[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8323,7 +8323,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional.composed[1]</t>
+          <t xml:space="preserve">injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8355,7 +8355,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional.composed[1]</t>
+          <t xml:space="preserve">release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8387,7 +8387,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8419,7 +8419,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.emotional.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8451,7 +8451,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8483,7 +8483,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.emotional.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8515,7 +8515,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.emotional.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8547,7 +8547,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.emotional.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8579,7 +8579,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8611,7 +8611,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8643,7 +8643,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8707,7 +8707,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8739,7 +8739,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -9123,7 +9123,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9155,7 +9155,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9187,7 +9187,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[2]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9219,7 +9219,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9251,7 +9251,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[2]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9283,7 +9283,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.composed[1]</t>
+          <t xml:space="preserve">survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9315,7 +9315,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.emotional.composed[2]</t>
+          <t xml:space="preserve">survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9347,7 +9347,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9379,7 +9379,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[2]</t>
+          <t xml:space="preserve">champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9411,7 +9411,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.composed[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9443,7 +9443,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.emotional.composed[2]</t>
+          <t xml:space="preserve">defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9475,7 +9475,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.composed[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9507,7 +9507,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.emotional.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.emotional.composed[2]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9539,7 +9539,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.emotional.composed[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9571,7 +9571,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.emotional.composed[1]</t>
+          <t xml:space="preserve">postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9603,7 +9603,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.emotional.composed[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9635,7 +9635,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.emotional.composed[1]</t>
+          <t xml:space="preserve">postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9667,7 +9667,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.emotional.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9699,7 +9699,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.emotional.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9731,7 +9731,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.emotional.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.emotional.composed[1]</t>
+          <t xml:space="preserve">summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9763,7 +9763,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9795,7 +9795,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9827,7 +9827,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.emotional.composed[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9859,7 +9859,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.emotional.composed[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9891,7 +9891,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.emotional.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.emotional.composed[1]</t>
+          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9923,7 +9923,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.emotional.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.emotional.composed[1]</t>
+          <t xml:space="preserve">result_win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9955,7 +9955,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9987,7 +9987,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.emotional.composed[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.emotional.composed[1]</t>
+          <t xml:space="preserve">fighter.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10019,7 +10019,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10051,7 +10051,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.emotional.composed[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…胸が苦しいな…でも、この痛みが生きてる証だから）</t>
+          <t xml:space="preserve">（うわ、胸が苦しい！ でも、これが生きてるってことだよね！）</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ひとりは、寂しかった。…仲間ができて、嬉しい</t>
+          <t xml:space="preserve">ひとりも気楽だったけどね！ やっぱり仲間がいるのが嬉しい！</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……切られても、こうして戦ってる。見えてたろ?</t>
+          <t xml:space="preserve">……切られても、こうして戦ってる。見えてたでしょ？</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{partner}、悪い。あたしが弱かった。…それだけだ。</t>
+          <t xml:space="preserve">…{partner}、悪い。私が弱かった。…それだけだ。</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は、こうはいかない。{partner}、もう一回だけ付き合ってくれ。</t>
+          <t xml:space="preserve">…次は、こうはいかない。{partner}、もう一回だけ付き合って。</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝手に幕を下ろすな。…まだ、こっちに残ってる</t>
+          <t xml:space="preserve">…勝手に幕を下ろさないで。…まだ、こっちに残ってる</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が押し殺した声で{nameA}に告げた。「…もういい。…覚えてろ」</t>
+          <t xml:space="preserve">{nameB}が押し殺した声で{nameA}に告げた。「…もういい。…覚えておいて」</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ふぅん。よく、わたしの名前を出せたね。</t>
+          <t xml:space="preserve">……ふぅん。よく、私の名前を出せたね。</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちっ。次は、こうはいかない。</t>
+          <t xml:space="preserve">……くっ。次は、こうはいかない。</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ……そうかよ。覚えておく。</t>
+          <t xml:space="preserve">……っ……そう。覚えておく。</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これで分かった? 次はないよ。</t>
+          <t xml:space="preserve">……これで分かった？ 次はないよ。</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…泣くなって。…こっちまで、困るだろ</t>
+          <t xml:space="preserve">…っ…泣くなって。…こっちまで、困るでしょ</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんだか壁を超えてみたいな。…へぇ、イイ感じじゃん♪</t>
+          <t xml:space="preserve">なんか、壁を超えられそうな気がする！ うん、これいい感じ！</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6204,14 +6204,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
+          <t xml:space="preserve">みんなでつかんだ勝利だ。誇らしいよ。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
+          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6268,14 +6268,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
+          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.emotional[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
+          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.emotional[1]</t>
+          <t xml:space="preserve">mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
+          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…言葉になりません</t>
+          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
+          <t xml:space="preserve">相棒と勝ててよかった。本当に、それだけで十分だ。</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[3]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合にします。絶対に</t>
+          <t xml:space="preserve">ドーム。…言葉になりません</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
+          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[2]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
+          <t xml:space="preserve">いい試合にします。絶対に</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[3]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6524,14 +6524,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます、本当に</t>
+          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6541,29 +6541,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、練習が楽しい。…もっとやりたいな</t>
+          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6573,29 +6573,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.emotional[2]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が動くようになってきた。…嬉しいよ</t>
+          <t xml:space="preserve">…ありがとうございます、本当に</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.emotional[1]</t>
+          <t xml:space="preserve">N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6620,14 +6620,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなのこと、好きだよ。…一緒にいられて幸せだ</t>
+          <t xml:space="preserve">…っ、練習が楽しい。…もっとやりたいな</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.emotional[1]</t>
+          <t xml:space="preserve">N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6652,14 +6652,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体がしんどいな。…でも、まだやりたいんだけど</t>
+          <t xml:space="preserve">…体が動くようになってきた。…嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.emotional[1]</t>
+          <t xml:space="preserve">N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんな応援してくれてるんだね。…ちょっと、泣きそうだ</t>
+          <t xml:space="preserve">…みんなのこと、好きだよ。…一緒にいられて幸せだ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.emotional[1]</t>
+          <t xml:space="preserve">N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、わからない。…どうすればいいんだろうね</t>
+          <t xml:space="preserve">…体がしんどいな。…でも、まだやりたいんだけど</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.emotional[1]</t>
+          <t xml:space="preserve">N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6748,14 +6748,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近、ずっと晴れないんだよね。…うまく言えないけど</t>
+          <t xml:space="preserve">…みんな応援してくれてるんだね。…ちょっと、泣きそうだ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった</t>
+          <t xml:space="preserve">…もう、わからない。…どうすればいいんだろうね</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いい</t>
+          <t xml:space="preserve">…最近、ずっと晴れないんだよね。…うまく言えないけど</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
+          <t xml:space="preserve">…っ…ここにいてよかった</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
+          <t xml:space="preserve">…っ…まあ、いい</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出番、まだかな</t>
+          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いいさ</t>
+          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.emotional[1]</t>
+          <t xml:space="preserve">G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…{name2}。…元気で</t>
+          <t xml:space="preserve">…っ…出番、まだかな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
+          <t xml:space="preserve">…っ…まあ、いいさ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…次は、こうはいかない</t>
+          <t xml:space="preserve">…っ…{name2}。…元気で</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7085,29 +7085,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……参ったな。これは、こたえるよ</t>
+          <t xml:space="preserve">…っ…次は、こうはいかない</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7117,29 +7117,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.emotional[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビか。…っ、…嬉しいね。やらせてもらうよ</t>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.emotional[1]</t>
+          <t xml:space="preserve">faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から話が来てるんだ。…どうしたものかな。正直、迷ってる</t>
+          <t xml:space="preserve">……参ったな。これは、こたえるよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.emotional[1]</t>
+          <t xml:space="preserve">E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7196,14 +7196,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…今日は、やらない</t>
+          <t xml:space="preserve">…テレビか。…っ、…嬉しいね。やらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.emotional[2]</t>
+          <t xml:space="preserve">E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出してもらえないのに練習して。…何になるのかな</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。…どうしたものかな。正直、迷ってる</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7260,14 +7260,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（感情を押し殺した声で「…もう限界かもね」と仲間にだけ漏らしている）</t>
+          <t xml:space="preserve">…もう無理だよ。…今日は、やらない</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7292,14 +7292,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに涙の絵文字と「…もう駄目かもしれないね」と投稿。静かな文面だけに騒ぎが大きくなっている）</t>
+          <t xml:space="preserve">…出してもらえないのに練習して。…何になるのかな</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.emotional[1]</t>
+          <t xml:space="preserve">S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7324,14 +7324,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頼むよ。ベルト、挑ませてほしい。…もう、待てないんだ</t>
+          <t xml:space="preserve">（感情を押し殺した声で「…もう限界かもね」と仲間にだけ漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.emotional[1]</t>
+          <t xml:space="preserve">S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人と、やらせてほしい。…これだけは、譲れないんだ</t>
+          <t xml:space="preserve">（SNSに涙の絵文字と「…もう駄目かもしれないね」と投稿。静かな文面だけに騒ぎが大きくなっている）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.emotional[1]</t>
+          <t xml:space="preserve">S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すまない。体が、もう限界でさ。…少し休ませてほしい</t>
+          <t xml:space="preserve">…頼むよ。ベルト、挑ませてほしい。…もう、待てないんだ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.emotional[1]</t>
+          <t xml:space="preserve">S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…このままなら、ここにはいられない</t>
+          <t xml:space="preserve">…あの人と、やらせてほしい。…これだけは、譲れないんだ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.emotional[1]</t>
+          <t xml:space="preserve">S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ（込み上げたものを飲み下し、静かに目を閉じた）</t>
+          <t xml:space="preserve">…すまない。体が、もう限界でさ。…少し休ませてほしい</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.emotional[1]</t>
+          <t xml:space="preserve">S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頼むよ。特訓させてほしい。…まだ、こんなもので終われないんだ</t>
+          <t xml:space="preserve">…もう無理だよ。…このままなら、ここにはいられない</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.emotional[1]</t>
+          <t xml:space="preserve">S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩に残せるものがあるなら、やらせてほしい。…それだけだよ</t>
+          <t xml:space="preserve">……っ（込み上げたものを飲み下し、静かに目を閉じた）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.emotional[1]</t>
+          <t xml:space="preserve">S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…すぐ治す。…早く戻りたいんだ</t>
+          <t xml:space="preserve">…頼むよ。特訓させてほしい。…まだ、こんなもので終われないんだ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.emotional[1]</t>
+          <t xml:space="preserve">S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…あの人といると、息が詰まる</t>
+          <t xml:space="preserve">…後輩に残せるものがあるなら、やらせてほしい。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.emotional[1]</t>
+          <t xml:space="preserve">B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私だって辛いんだよ。…わかってないだろうけど</t>
+          <t xml:space="preserve">…っ…すぐ治す。…早く戻りたいんだ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…コラボか。…どんな形になるんだろうね</t>
+          <t xml:space="preserve">…もう無理だよ。…あの人といると、息が詰まる</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7676,14 +7676,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…CMか。…緊張はする。…でもやるよ</t>
+          <t xml:space="preserve">…私だって辛いんだよ。…わかってないだろうけど</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…みんなに会えるんだ。…全員、笑顔にして帰すよ</t>
+          <t xml:space="preserve">…っ…コラボか。…どんな形になるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ランウェイか。…これは、緊張するやつだね</t>
+          <t xml:space="preserve">…っ…CMか。…緊張はする。…でもやるよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…グラビア。…私が、か。…参ったな</t>
+          <t xml:space="preserve">…っ…みんなに会えるんだ。…全員、笑顔にして帰すよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…バラエティか。…これは、少し楽しみだね</t>
+          <t xml:space="preserve">…っ…ランウェイか。…これは、緊張するやつだね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…私が、か。…やるよ</t>
+          <t xml:space="preserve">…っ…グラビア。…私が、か。…参ったな</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7853,29 +7853,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
+          <t xml:space="preserve">…っ…バラエティか。…これは、少し楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7885,29 +7885,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
+          <t xml:space="preserve">…っ…私が、か。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
@@ -7932,14 +7932,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
@@ -7964,14 +7964,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
@@ -7996,14 +7996,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8060,14 +8060,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝手に幕を下ろすな。…まだ、こっちに残ってる</t>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8092,14 +8092,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
+          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8124,14 +8124,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
+          <t xml:space="preserve">…勝手に幕を下ろさないで。…まだ、こっちに残ってる</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8156,14 +8156,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.emotional[1]</t>
+          <t xml:space="preserve">draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
+          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
+          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8540,14 +8540,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.emotional[1]</t>
+          <t xml:space="preserve">titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8636,14 +8636,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
@@ -8668,14 +8668,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
@@ -8764,14 +8764,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8781,29 +8781,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いい</t>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8813,29 +8813,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8860,14 +8860,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
+          <t xml:space="preserve">…っ…もう、いい</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8892,14 +8892,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
+          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8924,14 +8924,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
+          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8956,14 +8956,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
+          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8988,14 +8988,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…超える。…必ず</t>
+          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9020,14 +9020,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
+          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
+          <t xml:space="preserve">…っ…超える。…必ず</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いいかな</t>
+          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大丈夫、かな</t>
+          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
+          <t xml:space="preserve">…っ…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9165,29 +9165,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
+          <t xml:space="preserve">…っ…大丈夫、かな</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9197,29 +9197,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
+          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9244,14 +9244,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
+          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
+          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9308,14 +9308,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
+          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9340,14 +9340,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
+          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9372,14 +9372,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の勝利だ。一人では……ここには、到底たどり着けなかった</t>
+          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9389,12 +9389,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[2]</t>
+          <t xml:space="preserve">survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9404,14 +9404,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれた道を……最後まで歩けた。それが、何より……</t>
+          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9436,14 +9436,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は受け取ろう……だが、この胸の内は……次に晴らす他ない</t>
+          <t xml:space="preserve">これ、三人で獲った勝利だから！ ひとりだったら絶対ここまで来れてない！</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった……それだけが、今は重い。次こそ……全てを</t>
+          <t xml:space="preserve">みんなが繋いでくれたから、最後まで走りきれた！ それが一番嬉しい！</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9500,14 +9500,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">限界は何度も訪れた。それでも……足が前に出た。理屈ではなく、意地だった</t>
+          <t xml:space="preserve">賞はもらう！ でも正直、めちゃくちゃ悔しい！ これは次にぶつける！</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は壊れかけている。だが……最後に立っていた。それだけで、十分だ</t>
+          <t xml:space="preserve">足りなかった！ それがもう、悔しくて仕方ない！ 次こそ全部獲る！</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
+          <t xml:space="preserve">もう無理って何回も思った！ でも足が勝手に前に出た！ 理屈じゃない、意地！</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
+          <t xml:space="preserve">体はもうボロボロ！ でも最後に立ってたのはこっち！ それだけで満足！</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
+          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
+          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。…負けない</t>
+          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…やるよ</t>
+          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けない。…絶対に</t>
+          <t xml:space="preserve">…行くよ。…負けない</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
+          <t xml:space="preserve">…選ばれたか。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝負しよう。…本気で</t>
+          <t xml:space="preserve">…負けない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+          <t xml:space="preserve">…勝負しよう。…本気で</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9948,14 +9948,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…よかった</t>
+          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9980,14 +9980,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9997,29 +9997,29 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">result_win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+          <t xml:space="preserve">…っ…勝った。…よかった</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
@@ -10039,49 +10039,113 @@
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr" s="2">
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr" s="12">
+      <c r="D307" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr" s="2">
+      <c r="E307" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr" s="3">
+      <c r="F307" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H305"/>
+  <autoFilter ref="A1:H307"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3842,7 +3842,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3867,14 +3867,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ…ありがとう…ございます。…絶対、返すから…。</t>
+          <t xml:space="preserve">よし、分かった！ …うん、悔しいけどね。悔しいのは、まだやれる証拠だし！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_hold.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3899,14 +3899,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りない…けど…っ。…気持ちは、受け取ったから…。</t>
+          <t xml:space="preserve">……ずるいよ、社長！ そんなことされたら、下がるどころじゃ済まないじゃん！ …やってやる！</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やっぱり…っ…。……分かった…。</t>
+          <t xml:space="preserve">うわ、下がるんだ！ …いや、うん、そりゃそうだよね。分かってる、分かってるって！</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_strict.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}{record}……悔しくないって言ったら、嘘になるかな…っ。</t>
+          <t xml:space="preserve">……えっ、そこまで！？ ……いや、いい。言わない。今言ったら、絶対いいこと言えないから！</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ…。…分かった…。…悔しく、ないから…。</t>
+          <t xml:space="preserve">よし、これでいい！ ……自分で言って、自分で納得した。……なんか、すっきりしたかも！</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.emotional[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もういいよ。何も言う気はない。……さよなら。</t>
+          <t xml:space="preserve">……なんで下げてくれないの！ せっかく決心したのに！ ……うう、もう、頑張るしかないじゃん！</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.emotional[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。…けど、もうここにはいられないんだ。</t>
+          <t xml:space="preserve">社長！ 先に言う！ もう全盛期じゃない！ …だから下げて。ちゃんと、自分で言いたかったんだ。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.emotional[1]</t>
+          <t xml:space="preserve">raise_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…自分でも、どうしたいのか分からない。…ただ、このままじゃダメだって、それだけは。</t>
+          <t xml:space="preserve">…社長…っ…ありがとう…ございます。…絶対、返すから…。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.emotional[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ。{tenure}…ここにいたかった…けど…もう、いられない…。</t>
+          <t xml:space="preserve">……足りない…けど…っ。…気持ちは、受け取ったから…。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.emotional[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{tenure_farewell}…ここでの時間は、忘れないよ。{rivalry}…じゃあ、さよなら。</t>
+          <t xml:space="preserve">……やっぱり…っ…。……分かった…。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.emotional[1]</t>
+          <t xml:space="preserve">raise_open.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。…ありがとう。…でも…もう、戻れないんだ。…ごめん。</t>
+          <t xml:space="preserve">…社長。{tenure}{record}……悔しくないって言ったら、嘘になるかな…っ。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.emotional[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.emotional[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4219,271 +4219,271 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…っ…。…ありがとう…。…必ず、返すから…。</t>
+          <t xml:space="preserve">……っ…。…分かった…。…悔しく、ないから…。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もういいよ。何も言う気はない。……さよなら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.emotional[2]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.emotional[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しい。…けど、もうここにはいられないんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…自分でも、どうしたいのか分からない。…ただ、このままじゃダメだって、それだけは。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…っ。{tenure}…ここにいたかった…けど…もう、いられない…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{tenure_farewell}…ここでの時間は、忘れないよ。{rivalry}…じゃあ、さよなら。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。…ありがとう。…でも…もう、戻れないんだ。…ごめん。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長…っ…。…ありがとう…。…必ず、返すから…。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.emotional[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.composed.emotional[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここが好きなんだ。
 …悪いけど、その話は聞けない</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fail.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…ごめん。今は離れられない</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…引き抜き。…ふぅん。…聞くよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…っ…新しい場所か。…頑張るよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの子たち、ちゃんと抱えていてください。お願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメインは私たちに任せてください。今の状態を逃したくないんです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちが受け取っているもの、もう一度見直してください。お願いします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーがやってきたこと、しっかり見ていただきたい。</t>
-        </is>
-      </c>
-    </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4493,29 +4493,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">fail.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
+          <t xml:space="preserve">…ごめん。今は離れられない</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4525,29 +4525,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">start.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
+          <t xml:space="preserve">…引き抜き。…ふぅん。…聞くよ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4557,29 +4557,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">success.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
+          <t xml:space="preserve">…っ…新しい場所か。…頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4604,14 +4604,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。引き受けた重さ、噛み締めます。</t>
+          <t xml:space="preserve">社長、私たちの子たち、ちゃんと抱えていてください。お願いします。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4636,14 +4636,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…次は、必ず。</t>
+          <t xml:space="preserve">社長、次のメインは私たちに任せてください。今の状態を逃したくないんです。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
+          <t xml:space="preserve">社長、私たちが受け取っているもの、もう一度見直してください。お願いします。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4700,14 +4700,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…この決断、忘れません。ありがとうございます。</t>
+          <t xml:space="preserve">社長、私たちのメンバーがやってきたこと、しっかり見ていただきたい。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4732,14 +4732,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…次に、また。</t>
+          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
+          <t xml:space="preserve">社長、ありがとうございます。引き受けた重さ、噛み締めます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
+          <t xml:space="preserve">…そうですか。…次は、必ず。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ああ、…そうでしたか。…悪いことをしました。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないですね。</t>
+          <t xml:space="preserve">社長…この決断、忘れません。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4956,14 +4956,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですね、…悪かったです。</t>
+          <t xml:space="preserve">…そうですか。…次に、また。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4988,14 +4988,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
+          <t xml:space="preserve">社長…その一言で、随分と救われます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5052,14 +5052,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私、止まれませんから。</t>
+          <t xml:space="preserve">…そう、ですか。…わかりました。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、申し訳ありません。…次こそ、ちゃんと出ます。</t>
+          <t xml:space="preserve">…社長…そういう形でしたか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。</t>
+          <t xml:space="preserve">…ああ、…そうでしたか。…悪いことをしました。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5148,14 +5148,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…申し訳ないです、ありがたいです。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、誰かを置いてけぼりにはしたくないですね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5180,14 +5180,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…見ていてくださったんですね。ありがとうございます。</t>
+          <t xml:space="preserve">…そうですね、…悪かったです。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。…まだ、立っていられます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。一人で抱えなくていいんですね。</t>
+          <t xml:space="preserve">…そう、ですか。…私の熱、しまいます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5276,14 +5276,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…私の至らなさ、噛み締めます。</t>
+          <t xml:space="preserve">…ありがとうございます。…私、止まれませんから。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…社長、申し訳ありません。…次こそ、ちゃんと出ます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形で気にかけてくださるの、ありがたいです。</t>
+          <t xml:space="preserve">…社長…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5372,14 +5372,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。…私が、抑えきれていませんでした。</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…申し訳ないです、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5404,14 +5404,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…一度息を吸って、結局何も言わなかった）</t>
+          <t xml:space="preserve">…社長…見ていてくださったんですね。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5436,14 +5436,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
+          <t xml:space="preserve">…大丈夫です。…まだ、立っていられます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…そうですね。…私が、追い込みすぎていました。</t>
+          <t xml:space="preserve">…社長…ありがとうございます。一人で抱えなくていいんですね。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。やり切らせてください。</t>
+          <t xml:space="preserve">…そうですか。…私の至らなさ、噛み締めます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5532,14 +5532,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長…ありがとうございます。私、見えていませんでした。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5564,14 +5564,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">許せないね、あのやり方は</t>
+          <t xml:space="preserve">…社長…そういう形で気にかけてくださるの、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5596,14 +5596,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらも、引けないんだ</t>
+          <t xml:space="preserve">…そうですか。…私が、抑えきれていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5613,29 +5613,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか、壁を超えられそうな気がする！ うん、これいい感じ！</t>
+          <t xml:space="preserve">（…一度息を吸って、結局何も言わなかった）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5645,29 +5645,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…っ…体が、勝手に——…悪くない——）</t>
+          <t xml:space="preserve">…社長…そういう形ですか。…ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5677,29 +5677,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
+          <t xml:space="preserve">…社長…そうですね。…私が、追い込みすぎていました。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5709,29 +5709,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
+          <t xml:space="preserve">…ありがとうございます。やり切らせてください。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.emotional[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5741,29 +5741,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.composed.emotional[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
+          <t xml:space="preserve">…社長…ありがとうございます。私、見えていませんでした。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.attack.composed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5773,29 +5773,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.composed.emotional[1]</t>
+          <t xml:space="preserve">emotional.attack.composed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう伸びないんだ。…ちょっと寂しいけど、悪くない</t>
+          <t xml:space="preserve">許せないね、あのやり方は</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.emotional[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.emotional.defend.composed</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5805,29 +5805,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.composed.emotional[1]</t>
+          <t xml:space="preserve">emotional.defend.composed</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来れた…ちょっとだけ、ジーンと来ちゃった</t>
+          <t xml:space="preserve">こちらも、引けないんだ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.emotional[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5852,14 +5852,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ちょっと嬉しいかも…へへ</t>
+          <t xml:space="preserve">なんか、壁を超えられそうな気がする！ うん、これいい感じ！</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.emotional[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5884,14 +5884,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あはは、ダメだ。嬉しすぎて言葉にならない</t>
+          <t xml:space="preserve">（…っ…体が、勝手に——…悪くない——）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.emotional[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.emotional[1]</t>
+          <t xml:space="preserve">fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5916,14 +5916,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、こんなに見てくれてるんだ…ちょっと照れちゃうね</t>
+          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.emotional[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.emotional[1]</t>
+          <t xml:space="preserve">heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5948,14 +5948,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あぁ…ダメだ、こんなに応援されたら…泣いちゃう</t>
+          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5980,14 +5980,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いいかな。…何もしたくない</t>
+          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">cap_reached.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…また闘いたい。…大丈夫、もう大丈夫だ</t>
+          <t xml:space="preserve">…もう伸びないんだ。…ちょっと寂しいけど、悪くない</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6044,14 +6044,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やっと…抜け出せた。…もう大丈夫</t>
+          <t xml:space="preserve">ここまで来れた…ちょっとだけ、ジーンと来ちゃった</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.emotional[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…あの負けが…まだ、引っかかってる</t>
+          <t xml:space="preserve">わ、ちょっと嬉しいかも…へへ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.emotional[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…治ったのに。…なんで動けないんだ</t>
+          <t xml:space="preserve">…あはは、ダメだ。嬉しすぎて言葉にならない</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.emotional[1]</t>
+          <t xml:space="preserve">pop_growth.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6140,14 +6140,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…戻ってきた。…けど、体が少し…震える</t>
+          <t xml:space="preserve">わ、こんなに見てくれてるんだ…ちょっと照れちゃうね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.emotional[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.emotional[1]</t>
+          <t xml:space="preserve">pop_star.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6172,14 +6172,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…治ったのに。…この不安は何だろう</t>
+          <t xml:space="preserve">あぁ…ダメだ、こんなに応援されたら…泣いちゃう</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.emotional[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6189,29 +6189,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなでつかんだ勝利だ。誇らしいよ。</t>
+          <t xml:space="preserve">…っ…もう、いいかな。…何もしたくない</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6221,29 +6221,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
+          <t xml:space="preserve">…っ…また闘いたい。…大丈夫、もう大丈夫だ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6253,29 +6253,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
+          <t xml:space="preserve">…っ…やっと…抜け出せた。…もう大丈夫</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.emotional[1]</t>
+          <t xml:space="preserve">defeat.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
+          <t xml:space="preserve">…っ…あの負けが…まだ、引っかかってる</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6317,29 +6317,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.emotional[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
+          <t xml:space="preserve">…っ…治ったのに。…なんで動けないんだ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6349,29 +6349,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.emotional[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
+          <t xml:space="preserve">…っ…戻ってきた。…けど、体が少し…震える</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.emotional[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6381,29 +6381,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.emotional[1]</t>
+          <t xml:space="preserve">penalty_end.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と勝ててよかった。本当に、それだけで十分だ。</t>
+          <t xml:space="preserve">…っ…治ったのに。…この不安は何だろう</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。…言葉になりません</t>
+          <t xml:space="preserve">みんなでつかんだ勝利だ。誇らしいよ。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[2]</t>
+          <t xml:space="preserve">bestMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
+          <t xml:space="preserve">…っ…あの試合は…ちょっと、特別だったね。…うん</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[3]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6492,14 +6492,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合にします。絶対に</t>
+          <t xml:space="preserve">…っ…このベルト…簡単には、渡さないよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6524,14 +6524,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
+          <t xml:space="preserve">…っ…みんな、ありがとう。…いい場所だった。…本当に</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[2]</t>
+          <t xml:space="preserve">mvp.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
+          <t xml:space="preserve">…っ…一年間、苦しかったけど…ま、報われたかな。…うん</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[3]</t>
+          <t xml:space="preserve">rookie.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6588,14 +6588,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます、本当に</t>
+          <t xml:space="preserve">…っ…そうか。…ありがとう。…次、行くよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6605,29 +6605,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.emotional[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ、練習が楽しい。…もっとやりたいな</t>
+          <t xml:space="preserve">相棒と勝ててよかった。本当に、それだけで十分だ。</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6637,29 +6637,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.emotional[2]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が動くようになってきた。…嬉しいよ</t>
+          <t xml:space="preserve">ドーム。…言葉になりません</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6669,29 +6669,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなのこと、好きだよ。…一緒にいられて幸せだ</t>
+          <t xml:space="preserve">…この感情を、試合にぶつけます</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6701,29 +6701,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体がしんどいな。…でも、まだやりたいんだけど</t>
+          <t xml:space="preserve">いい試合にします。絶対に</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6733,29 +6733,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんな応援してくれてるんだね。…ちょっと、泣きそうだ</t>
+          <t xml:space="preserve">…満員。胸が、いっぱいです</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6765,29 +6765,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、わからない。…どうすればいいんだろうね</t>
+          <t xml:space="preserve">…落ち着かせてください、少しだけ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.emotional[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.emotional[3]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6797,29 +6797,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[3]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近、ずっと晴れないんだよね。…うまく言えないけど</t>
+          <t xml:space="preserve">…ありがとうございます、本当に</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった</t>
+          <t xml:space="preserve">…っ、練習が楽しい。…もっとやりたいな</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N1.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いい</t>
+          <t xml:space="preserve">…体が動くようになってきた。…嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
+          <t xml:space="preserve">…みんなのこと、好きだよ。…一緒にいられて幸せだ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6940,14 +6940,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
+          <t xml:space="preserve">…体がしんどいな。…でも、まだやりたいんだけど</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6972,14 +6972,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出番、まだかな</t>
+          <t xml:space="preserve">…みんな応援してくれてるんだね。…ちょっと、泣きそうだ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">N5_low.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7004,14 +7004,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、いいさ</t>
+          <t xml:space="preserve">…もう、わからない。…どうすればいいんだろうね</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.emotional[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.emotional[1]</t>
+          <t xml:space="preserve">N5_warning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…{name2}。…元気で</t>
+          <t xml:space="preserve">…最近、ずっと晴れないんだよね。…うまく言えないけど</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7068,14 +7068,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
+          <t xml:space="preserve">…っ…ここにいてよかった</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">G1.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…次は、こうはいかない</t>
+          <t xml:space="preserve">…っ…まあ、いい</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.emotional[1]</t>
+          <t xml:space="preserve">G2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…っ…先にいたのは、こっちなのに</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7149,29 +7149,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.emotional[1]</t>
+          <t xml:space="preserve">G3.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……参ったな。これは、こたえるよ</t>
+          <t xml:space="preserve">…っ…黙ってるけど。…悔しくないわけじゃない</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7181,29 +7181,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.emotional[1]</t>
+          <t xml:space="preserve">G4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビか。…っ、…嬉しいね。やらせてもらうよ</t>
+          <t xml:space="preserve">…っ…出番、まだかな</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7213,29 +7213,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.emotional[1]</t>
+          <t xml:space="preserve">R2.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所から話が来てるんだ。…どうしたものかな。正直、迷ってる</t>
+          <t xml:space="preserve">…っ…まあ、いいさ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7245,29 +7245,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.emotional[1]</t>
+          <t xml:space="preserve">R3.modal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…今日は、やらない</t>
+          <t xml:space="preserve">…っ…{name2}。…元気で</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7277,29 +7277,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.emotional[2]</t>
+          <t xml:space="preserve">R4.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出してもらえないのに練習して。…何になるのかな</t>
+          <t xml:space="preserve">…っ…勝った。…うん、勝った</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7309,29 +7309,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.emotional[1]</t>
+          <t xml:space="preserve">R5.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（感情を押し殺した声で「…もう限界かもね」と仲間にだけ漏らしている）</t>
+          <t xml:space="preserve">…っ…次は、こうはいかない</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7341,29 +7341,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.emotional[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに涙の絵文字と「…もう駄目かもしれないね」と投稿。静かな文面だけに騒ぎが大きくなっている）</t>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.emotional[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.emotional[1]</t>
+          <t xml:space="preserve">faction_decree.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7388,14 +7388,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頼むよ。ベルト、挑ませてほしい。…もう、待てないんだ</t>
+          <t xml:space="preserve">……参ったな。これは、こたえるよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.emotional[1]</t>
+          <t xml:space="preserve">E1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7420,14 +7420,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人と、やらせてほしい。…これだけは、譲れないんだ</t>
+          <t xml:space="preserve">…テレビか。…っ、…嬉しいね。やらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.emotional[1]</t>
+          <t xml:space="preserve">E6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7452,14 +7452,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…すまない。体が、もう限界でさ。…少し休ませてほしい</t>
+          <t xml:space="preserve">…他所から話が来てるんだ。…どうしたものかな。正直、迷ってる</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7484,14 +7484,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…このままなら、ここにはいられない</t>
+          <t xml:space="preserve">…もう無理だよ。…今日は、やらない</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.emotional[1]</t>
+          <t xml:space="preserve">S_boycott.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7516,14 +7516,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……っ（込み上げたものを飲み下し、静かに目を閉じた）</t>
+          <t xml:space="preserve">…出してもらえないのに練習して。…何になるのかな</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.emotional[1]</t>
+          <t xml:space="preserve">S_grumble.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7548,14 +7548,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頼むよ。特訓させてほしい。…まだ、こんなもので終われないんだ</t>
+          <t xml:space="preserve">（感情を押し殺した声で「…もう限界かもね」と仲間にだけ漏らしている）</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.emotional[1]</t>
+          <t xml:space="preserve">S_sns.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7580,14 +7580,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩に残せるものがあるなら、やらせてほしい。…それだけだよ</t>
+          <t xml:space="preserve">（SNSに涙の絵文字と「…もう駄目かもしれないね」と投稿。静かな文面だけに騒ぎが大きくなっている）</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.emotional[1]</t>
+          <t xml:space="preserve">S1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7612,14 +7612,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…すぐ治す。…早く戻りたいんだ</t>
+          <t xml:space="preserve">…頼むよ。ベルト、挑ませてほしい。…もう、待てないんだ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.emotional[1]</t>
+          <t xml:space="preserve">S2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう無理だよ。…あの人といると、息が詰まる</t>
+          <t xml:space="preserve">…あの人と、やらせてほしい。…これだけは、譲れないんだ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.emotional[1]</t>
+          <t xml:space="preserve">S3.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7676,14 +7676,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私だって辛いんだよ。…わかってないだろうけど</t>
+          <t xml:space="preserve">…すまない。体が、もう限界でさ。…少し休ませてほしい</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.emotional[1]</t>
+          <t xml:space="preserve">S4_direct.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7708,14 +7708,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…コラボか。…どんな形になるんだろうね</t>
+          <t xml:space="preserve">…もう無理だよ。…このままなら、ここにはいられない</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.emotional[1]</t>
+          <t xml:space="preserve">S4_silent.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…CMか。…緊張はする。…でもやるよ</t>
+          <t xml:space="preserve">……っ（込み上げたものを飲み下し、静かに目を閉じた）</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.emotional[1]</t>
+          <t xml:space="preserve">S5.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7772,14 +7772,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…みんなに会えるんだ。…全員、笑顔にして帰すよ</t>
+          <t xml:space="preserve">…頼むよ。特訓させてほしい。…まだ、こんなもので終われないんだ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.emotional[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.emotional[1]</t>
+          <t xml:space="preserve">S6.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ランウェイか。…これは、緊張するやつだね</t>
+          <t xml:space="preserve">…後輩に残せるものがあるなら、やらせてほしい。…それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.emotional[1]</t>
+          <t xml:space="preserve">B1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7836,14 +7836,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…グラビア。…私が、か。…参ったな</t>
+          <t xml:space="preserve">…っ…すぐ治す。…早く戻りたいんだ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…バラエティか。…これは、少し楽しみだね</t>
+          <t xml:space="preserve">…もう無理だよ。…あの人といると、息が詰まる</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.emotional[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…私が、か。…やるよ</t>
+          <t xml:space="preserve">…私だって辛いんだよ。…わかってないだろうけど</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7917,29 +7917,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_brand.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
+          <t xml:space="preserve">…っ…コラボか。…どんな形になるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7949,29 +7949,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_cm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
+          <t xml:space="preserve">…っ…CMか。…緊張はする。…でもやるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7981,29 +7981,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_fan.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">…っ…みんなに会えるんだ。…全員、笑顔にして帰すよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8013,29 +8013,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…っ…ランウェイか。…これは、緊張するやつだね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8045,29 +8045,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…っ…グラビア。…私が、か。…参ったな</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8077,29 +8077,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.emotional[1]</t>
+          <t xml:space="preserve">B4_variety.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
+          <t xml:space="preserve">…っ…バラエティか。…これは、少し楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.emotional[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8109,29 +8109,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.emotional[1]</t>
+          <t xml:space="preserve">B4.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝手に幕を下ろさないで。…まだ、こっちに残ってる</t>
+          <t xml:space="preserve">…っ…私が、か。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8163,7 +8163,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8195,7 +8195,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8220,14 +8220,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
+          <t xml:space="preserve">…勝ったのに、まだ腹が煮えてる。…笑えないな</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.emotional[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8348,14 +8348,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
+          <t xml:space="preserve">…勝手に幕を下ろさないで。…まだ、こっちに残ってる</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.emotional[1]</t>
+          <t xml:space="preserve">draftInterest.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8380,14 +8380,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
+          <t xml:space="preserve">…っ…選んでくれたら、全力で応える</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.emotional[1]</t>
+          <t xml:space="preserve">draftJoin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
+          <t xml:space="preserve">…っ…ずっと、この日を待ってた。頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.emotional[1]</t>
+          <t xml:space="preserve">faGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">faSigning.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8476,14 +8476,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
+          <t xml:space="preserve">…っ…ありがとう。全力でやる</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.emotional[1]</t>
+          <t xml:space="preserve">faWelcome.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8508,14 +8508,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
+          <t xml:space="preserve">…っ…嬉しい。よろしく</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8540,14 +8540,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…体は軽い。…こういう日は、黙って積むよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…体が重い。…今日は、腹が立つほど何も入らない</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.emotional[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…おかしいな。…同じことをして、同じに戻らない</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.emotional[1]</t>
+          <t xml:space="preserve">injury.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8636,14 +8636,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…悔しい。でも、必ず戻る</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">release.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8675,7 +8675,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8707,7 +8707,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
+          <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8764,14 +8764,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…守れた。…よかった</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">titleDefense.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8813,12 +8813,12 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">titleLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8828,14 +8828,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8845,29 +8845,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いい</t>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8877,29 +8877,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
+          <t xml:space="preserve">…っ…ありがとう。忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8909,29 +8909,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
+          <t xml:space="preserve">…っ…短い間だけど、全力で</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8941,29 +8941,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、諦めない</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8973,29 +8973,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
+          <t xml:space="preserve">…っ…守れた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9005,29 +9005,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
+          <t xml:space="preserve">…っ…ベルトが…。…取り戻す</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9037,29 +9037,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…超える。…必ず</t>
+          <t xml:space="preserve">…っ…チャンピオン。…嬉しい</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9084,14 +9084,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
+          <t xml:space="preserve">…っ…もう、いい</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9116,14 +9116,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
+          <t xml:space="preserve">…っ…まあ、仕方ないか</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9148,14 +9148,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…もう、いいかな</t>
+          <t xml:space="preserve">…っ…大事な存在だ。…うん</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9180,14 +9180,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…大丈夫、かな</t>
+          <t xml:space="preserve">…っ…出会えてよかった。…本当に</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">rivalry_29_down.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
+          <t xml:space="preserve">…っ…終わったか。…少し寂しいな</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9229,29 +9229,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">rivalry_30_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
+          <t xml:space="preserve">…っ…負けるわけにはいかない</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9261,29 +9261,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">rivalry_50_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
+          <t xml:space="preserve">…っ…超える。…必ず</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9293,29 +9293,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">rivalry_70_up.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
+          <t xml:space="preserve">…っ…この人がいなければ今の私はいない</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9325,29 +9325,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">trust_above_75.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
+          <t xml:space="preserve">…っ…ここにいてよかった。…みんな、ありがとう</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9357,29 +9357,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">trust_below_20.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
+          <t xml:space="preserve">…っ…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.emotional.composed[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9389,29 +9389,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">trust_below_35.emotional.composed[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
+          <t xml:space="preserve">…っ…大丈夫、かな</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9421,29 +9421,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ、三人で獲った勝利だから！ ひとりだったら絶対ここまで来れてない！</t>
+          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[2]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなが繋いでくれたから、最後まで走りきれた！ それが一番嬉しい！</t>
+          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9500,14 +9500,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらう！ でも正直、めちゃくちゃ悔しい！ これは次にぶつける！</t>
+          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった！ それがもう、悔しくて仕方ない！ 次こそ全部獲る！</t>
+          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理って何回も思った！ でも足が勝手に前に出た！ 理屈じゃない、意地！</t>
+          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体はもうボロボロ！ でも最後に立ってたのはこっち！ それだけで満足！</t>
+          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
+          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
+          <t xml:space="preserve">これ、三人で獲った勝利だから！ ひとりだったら絶対ここまで来れてない！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
+          <t xml:space="preserve">みんなが繋いでくれたから、最後まで走りきれた！ それが一番嬉しい！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
+          <t xml:space="preserve">賞はもらう！ でも正直、めちゃくちゃ悔しい！ これは次にぶつける！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
+          <t xml:space="preserve">足りなかった！ それがもう、悔しくて仕方ない！ 次こそ全部獲る！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。…負けない</t>
+          <t xml:space="preserve">もう無理って何回も思った！ でも足が勝手に前に出た！ 理屈じゃない、意地！</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…やるよ</t>
+          <t xml:space="preserve">体はもうボロボロ！ でも最後に立ってたのはこっち！ それだけで満足！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けない。…絶対に</t>
+          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝負しよう。…本気で</t>
+          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9948,14 +9948,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9980,14 +9980,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10012,14 +10012,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…よかった</t>
+          <t xml:space="preserve">…行くよ。…負けない</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10044,14 +10044,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…選ばれたか。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10061,29 +10061,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+          <t xml:space="preserve">…負けない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
@@ -10103,49 +10103,273 @@
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝負しよう。…本気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr" s="2">
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr" s="12">
+      <c r="D314" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr" s="2">
+      <c r="E314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr" s="3">
+      <c r="F314" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H307"/>
+  <autoFilter ref="A1:H314"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -296,7 +296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9187,7 +9187,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
+          <t xml:space="preserve">…っ…認める。…いい試合だった</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9229,29 +9229,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
+          <t xml:space="preserve">…っ…最高だ。…泣きそう</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9261,29 +9261,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
+          <t xml:space="preserve">GL-01.loss.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
+          <t xml:space="preserve">…っ…悔しい</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9293,29 +9293,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">GL-01.win.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
+          <t xml:space="preserve">…っ…勝てた。…よかった</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9325,29 +9325,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
+          <t xml:space="preserve">GL-02.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
+          <t xml:space="preserve">…っ…まだやれる</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9357,29 +9357,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[1]</t>
+          <t xml:space="preserve">GL-03.down.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
+          <t xml:space="preserve">…っ…何か変だ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9389,29 +9389,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.emotional[2]</t>
+          <t xml:space="preserve">GL-03.up.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
+          <t xml:space="preserve">…っ…嬉しいな</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9421,29 +9421,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ、三人で獲った勝利だから！ ひとりだったら絶対ここまで来れてない！</t>
+          <t xml:space="preserve">…っ…終わったか。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9453,12 +9453,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[2]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9468,14 +9468,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなが繋いでくれたから、最後まで走りきれた！ それが一番嬉しい！</t>
+          <t xml:space="preserve">…ここまで来た。…痛みは、後だ。…最後、やる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9500,14 +9500,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらう！ でも正直、めちゃくちゃ悔しい！ これは次にぶつける！</t>
+          <t xml:space="preserve">…身体は限界か。…かまわない。…立てる</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.emotional[2]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9532,14 +9532,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足りなかった！ それがもう、悔しくて仕方ない！ 次こそ全部獲る！</t>
+          <t xml:space="preserve">…相手は誰だ。…言葉はいらない。来たら、倒す</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9564,14 +9564,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう無理って何回も思った！ でも足が勝手に前に出た！ 理屈じゃない、意地！</t>
+          <t xml:space="preserve">…この一戦で、始まる。…かかってこい</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
+          <t xml:space="preserve">survivor.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9596,14 +9596,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体はもうボロボロ！ でも最後に立ってたのはこっち！ それだけで満足！</t>
+          <t xml:space="preserve">…一人、落とした。…息は上がってる。…でも、退かない。次、来い</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.emotional[1]</t>
+          <t xml:space="preserve">survivor.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
+          <t xml:space="preserve">…まだ立ってる。…言葉はいらない。…次を出せ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
+          <t xml:space="preserve">これ、三人で獲った勝利だから！ ひとりだったら絶対ここまで来れてない！</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
+          <t xml:space="preserve">みんなが繋いでくれたから、最後まで走りきれた！ それが一番嬉しい！</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.emotional[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9724,14 +9724,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
+          <t xml:space="preserve">賞はもらう！ でも正直、めちゃくちゃ悔しい！ これは次にぶつける！</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
+          <t xml:space="preserve">defiant.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
+          <t xml:space="preserve">足りなかった！ それがもう、悔しくて仕方ない！ 次こそ全部獲る！</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9788,14 +9788,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。…負けない</t>
+          <t xml:space="preserve">もう無理って何回も思った！ でも足が勝手に前に出た！ 理屈じゃない、意地！</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.emotional[1]</t>
+          <t xml:space="preserve">gauntlet.composed.emotional[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…やるよ</t>
+          <t xml:space="preserve">体はもうボロボロ！ でも最後に立ってたのはこっち！ それだけで満足！</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">champion.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けない。…絶対に</t>
+          <t xml:space="preserve">…っ…優勝か。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postLose.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9884,14 +9884,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
+          <t xml:space="preserve">…っ…悔しい。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝負しよう。…本気で</t>
+          <t xml:space="preserve">…一つ勝った。…まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">postWin.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9948,14 +9948,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+          <t xml:space="preserve">…いい大会だった。…忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
+          <t xml:space="preserve">preFinal.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9980,14 +9980,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+          <t xml:space="preserve">…決勝か。…ここまで来た以上、負けない</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.emotional[1]</t>
+          <t xml:space="preserve">preMatch.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10012,14 +10012,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…よかった</t>
+          <t xml:space="preserve">…行くよ。…負けない</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.emotional[1]</t>
+          <t xml:space="preserve">summon.composed.emotional[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10044,14 +10044,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+          <t xml:space="preserve">…選ばれたか。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10061,29 +10061,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+          <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+          <t xml:space="preserve">…負けない。…絶対に</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.emotional[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
@@ -10103,49 +10103,273 @@
       </c>
       <c r="E306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+          <t xml:space="preserve">…っ…やった。…ここまで、長かった</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝負しよう。…本気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…覚えておくよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…この悔しさは、覚えておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…よかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…勝った。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…ここまで来れた。…最高だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.emotional[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…っ…まだ終わってなかった。…やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.emotional[1]</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr" s="2">
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr" s="12">
+      <c r="D314" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.emotional[1]</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr" s="2">
+      <c r="E314" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr" s="3">
+      <c r="F314" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…っ…選んでくれたんなら。…応えるつもりだよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H307"/>
+  <autoFilter ref="A1:H314"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×感情的.xlsx
@@ -2299,7 +2299,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人のことが、まだ腹の底に残ってます。やらせてください。</t>
+          <t xml:space="preserve">社長。…あの団体が、まだ腹の底に残ってます。三人で行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっと呑み込んできました。もう限界です。あいつと、やらせてください。</t>
+          <t xml:space="preserve">…ずっと呑み込んできました。もう限界です。三人で行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…静かに言いますけど、本気です。あの人と、やらせてください。</t>
+          <t xml:space="preserve">社長。…静かに言いますけど、本気です。三人で、行かせてください。</t>
         </is>
       </c>
     </row>
